--- a/files/九龙-启德-天玺．海第1期.xlsx
+++ b/files/九龙-启德-天玺．海第1期.xlsx
@@ -8,13 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座 销控表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座 销控表" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mansion 1 销控表" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mansion 2 销控表" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -117,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -182,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -198,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1954,7 +1809,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -13098,3916 +12953,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天玺．海第1期 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>42 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>22 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>V. MANOR</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>V. SKYPLEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>27&amp;28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>V. SKYPLEX | 3533呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>V. MANOR | 2687呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 2106呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>A | 2141呎 (4+房)
-$13,916万
-$65,000/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 2144呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A | 2175呎 (4+房)
-$12,000万
-$55,172/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>A | 2187呎 (4+房)
-$12,089万
-$55,276/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-$6,663万
-$47,325/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr"/>
-      <c r="E12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 2194呎 (4+房)
-$11,672万
-$53,200/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr"/>
-      <c r="E13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 2196呎 (4+房)
-$11,931万
-$54,330/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr"/>
-      <c r="E14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 2192呎 (4+房)
-$11,903万
-$54,300/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-$6,970万
-$49,500/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 2183呎 (4+房)
-$11,635万
-$53,300/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-$6,054万
-$43,000/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr"/>
-      <c r="E16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 2171呎 (4+房)
-$11,545万
-$53,180/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-$5,984万
-$42,500/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr"/>
-      <c r="E17" s="16" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 2157呎 (4+房)
-$11,356万
-$52,646/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr"/>
-      <c r="E18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 2143呎 (4+房)
-$11,529万
-$53,800/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-$6,619万
-$47,010/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr"/>
-      <c r="E19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 2129呎 (4+房)
-$10,928万
-$51,329/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-$6,786万
-$48,200/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr"/>
-      <c r="E20" s="16" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 2115呎 (4+房)
-$10,300万
-$48,700/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-$5,892万
-$41,844/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr"/>
-      <c r="E21" s="16" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 2103呎 (4+房)
-$11,551万
-$54,927/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr"/>
-      <c r="E22" s="16" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 2096呎 (4+房)
-$12,164万
-$58,033/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr"/>
-      <c r="E23" s="16" t="inlineStr"/>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>A | 2093呎 (4+房)
-$11,822万
-$56,484/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr"/>
-      <c r="E24" s="16" t="inlineStr"/>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>A | 2093呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr"/>
-      <c r="E25" s="16" t="inlineStr"/>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 2093呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr"/>
-      <c r="E26" s="16" t="inlineStr"/>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 2093呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr"/>
-      <c r="E27" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天玺．海第1期 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>73 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>54 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>SKY MANOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 555呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-$3,346万
-$30,310/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-$3,312万
-$30,000/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr"/>
-      <c r="F10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr"/>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>SKY MANOR | 998呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 560呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 789呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 560呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 789呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 560呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 789呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 560呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 789呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-$3,950万
-$35,779/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 560呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 789呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 560呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 789呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 560呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 789呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 560呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 789呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 560呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 789呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 560呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 789呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 560呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 789呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 560呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 789呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr"/>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 560呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 789呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr"/>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 560呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 789呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr"/>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 560呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 789呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天玺．海第1期 - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>44 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>34 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>6 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>SKY MANOR</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>SKYPLEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>SKYPLEX | 2190呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>SKY MANOR | 2191呎 (4+房)
-$14,887万
-$67,946/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-$4,281万
-$38,022/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-$4,636万
-$42,571/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-$4,135万
-$36,723/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-$3,780万
-$34,711/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-$4,010万
-$35,613/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-$4,487万
-$41,201/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-$4,120万
-$36,590/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-$3,907万
-$35,875/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-$4,175万
-$37,075/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-$3,719万
-$34,151/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr"/>
-      <c r="E12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-$4,296万
-$38,156/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-$3,897万
-$35,781/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr"/>
-      <c r="E13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-$4,238万
-$37,638/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-$3,664万
-$33,650/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr"/>
-      <c r="E14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-$4,179万
-$37,114/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-$3,858万
-$35,425/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-$4,000万
-$35,524/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-$3,572万
-$32,801/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr"/>
-      <c r="E16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-$4,132万
-$36,701/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-$3,539万
-$32,500/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr"/>
-      <c r="E17" s="16" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-$3,892万
-$34,563/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-$3,529万
-$32,405/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr"/>
-      <c r="E18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-$3,738万
-$33,197/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-$3,508万
-$32,209/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr"/>
-      <c r="E19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-$3,956万
-$35,133/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-$3,768万
-$34,601/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr"/>
-      <c r="E20" s="16" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-$3,929万
-$34,898/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-$3,700万
-$33,976/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr"/>
-      <c r="E21" s="16" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-$3,850万
-$34,192/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-$3,659万
-$33,600/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr"/>
-      <c r="E22" s="16" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-$3,378万
-$30,000/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-$3,200万
-$29,385/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr"/>
-      <c r="E23" s="16" t="inlineStr"/>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-$3,278万
-$29,115/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr"/>
-      <c r="E24" s="16" t="inlineStr"/>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr"/>
-      <c r="E25" s="16" t="inlineStr"/>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr"/>
-      <c r="E26" s="16" t="inlineStr"/>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr"/>
-      <c r="E27" s="16" t="inlineStr"/>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 1126呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr"/>
-      <c r="E28" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天玺．海第1期 - 5座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>43 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>38 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>SKYPLEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>27&amp;28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>SKYPLEX | 3156呎 (4+房)
-$23,039万
-$73,000/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$7,155万
-$51,069/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$7,117万
-$50,800/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$6,939万
-$50,800/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$6,761万
-$48,256/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$6,592万
-$48,256/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$6,487万
-$46,300/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$6,325万
-$46,300/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$6,994万
-$49,920/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$6,672万
-$48,842/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$6,725万
-$48,000/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$6,557万
-$48,000/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$6,573万
-$46,915/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$6,628万
-$48,521/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$6,319万
-$45,100/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$7,035万
-$51,503/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$6,306万
-$45,007/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$6,112万
-$44,746/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$6,486万
-$46,298/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$6,324万
-$46,298/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$6,345万
-$45,291/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$6,187万
-$45,291/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$5,996万
-$42,800/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$7,121万
-$52,128/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$5,772万
-$41,200/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$6,761万
-$49,492/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$6,598万
-$47,095/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$6,198万
-$45,375/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$5,229万
-$37,323/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$6,031万
-$44,153/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$6,304万
-$45,000/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$4,868万
-$35,637/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$6,650万
-$47,466/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$6,247万
-$45,731/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr"/>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$6,969万
-$49,742/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$6,726万
-$49,239/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr"/>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-$6,641万
-$47,400/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-$6,448万
-$47,200/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr"/>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr"/>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 1366呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天玺．海第1期 - 6座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>43 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>43 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>SKYPLEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>27&amp;28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>SKYPLEX | 3203呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr"/>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr"/>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr"/>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr"/>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 1401呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 1374呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天玺．海第1期 - Mansion 1 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>SKY MANOR</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>SKYPLEX</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>V. HOUSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5&amp;6/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>SKYPLEX | 2437呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2&amp;3/F</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>SKY MANOR | 3099呎 (4+房)
-$24,792万
-$80,000/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>B1&amp;G&amp;1-3/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>V. HOUSE | 4395呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天玺．海第1期 - Mansion 2 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>8 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>8 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>H. HOUSE</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>MANOR A</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>MANOR B</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>MANOR C</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>SKYPLEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>SKYPLEX | 2214呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5&amp;6/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 1676呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 2034呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>MANOR C | 2090呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2&amp;3/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 1676呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 2114呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>MANOR C | 1986呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>B1&amp;G&amp;1-3/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>H. HOUSE | 4608呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr"/>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-启德-天玺．海第1期.xlsx
+++ b/files/九龙-启德-天玺．海第1期.xlsx
@@ -8,6 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mansion 1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mansion 2" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +48,102 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +154,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +235,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +668,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -12953,4 +13147,3916 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>V. MANOR</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>V. SKYPLEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>V. SKYPLEX | 3533呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>V. MANOR | 2687呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 2106呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 2141呎 (4+房)
+$13916万
+$65,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 2144呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 2175呎 (4+房)
+$12000万
+$55,172/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 2187呎 (4+房)
+$12089万
+$55,276/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+$6663万
+$47,325/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 2194呎 (4+房)
+$11672万
+$53,200/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 2196呎 (4+房)
+$11931万
+$54,330/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 2192呎 (4+房)
+$11903万
+$54,300/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+$6970万
+$49,500/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 2183呎 (4+房)
+$11635万
+$53,300/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+$6054万
+$43,000/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 2171呎 (4+房)
+$11545万
+$53,180/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+$5984万
+$42,500/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 2157呎 (4+房)
+$11356万
+$52,646/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr"/>
+      <c r="E17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 2143呎 (4+房)
+$11529万
+$53,800/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+$6619万
+$47,010/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 2129呎 (4+房)
+$10928万
+$51,329/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+$6786万
+$48,200/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="20" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 2115呎 (4+房)
+$10300万
+$48,700/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+$5892万
+$41,844/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr"/>
+      <c r="E20" s="20" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 2103呎 (4+房)
+$11551万
+$54,927/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr"/>
+      <c r="E21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 2096呎 (4+房)
+$12164万
+$58,033/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr"/>
+      <c r="E22" s="20" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 2093呎 (4+房)
+$11822万
+$56,484/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr"/>
+      <c r="E23" s="20" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>A | 2093呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr"/>
+      <c r="E24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 2093呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr"/>
+      <c r="E25" s="20" t="inlineStr"/>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 2093呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr"/>
+      <c r="E26" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>SKY MANOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 555呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+$3346万
+$30,310/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+$3312万
+$30,000/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>SKY MANOR | 998呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 789呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 789呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 789呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 789呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+$3950万
+$35,779/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 789呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 789呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 789呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 789呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 789呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 789呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 789呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 789呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 789呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 789呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 789呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>SKY MANOR</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>SKYPLEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>SKYPLEX | 2190呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>SKY MANOR | 2191呎 (4+房)
+$14887万
+$67,946/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+$4281万
+$38,022/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+$4636万
+$42,571/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+$4135万
+$36,723/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+$3780万
+$34,711/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+$4010万
+$35,613/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+$4487万
+$41,201/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+$4120万
+$36,590/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+$3907万
+$35,875/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+$4175万
+$37,075/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+$3719万
+$34,151/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+$4296万
+$38,156/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+$3897万
+$35,781/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+$4238万
+$37,638/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+$3664万
+$33,650/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+$4179万
+$37,114/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+$3858万
+$35,425/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+$4000万
+$35,524/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+$3572万
+$32,801/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+$4132万
+$36,701/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+$3539万
+$32,500/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+$3892万
+$34,563/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+$3529万
+$32,405/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr"/>
+      <c r="E17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+$3738万
+$33,197/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+$3508万
+$32,209/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+$3956万
+$35,133/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+$3768万
+$34,601/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="20" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+$3929万
+$34,898/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+$3700万
+$33,976/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr"/>
+      <c r="E20" s="20" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+$3850万
+$34,192/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+$3659万
+$33,600/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr"/>
+      <c r="E21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+$3378万
+$30,000/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+$3200万
+$29,385/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr"/>
+      <c r="E22" s="20" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+$3278万
+$29,115/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr"/>
+      <c r="E23" s="20" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr"/>
+      <c r="E24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr"/>
+      <c r="E25" s="20" t="inlineStr"/>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr"/>
+      <c r="E26" s="20" t="inlineStr"/>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr"/>
+      <c r="E27" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>SKYPLEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>SKYPLEX | 3156呎 (4+房)
+$23039万
+$73,000/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$7155万
+$51,069/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$7117万
+$50,800/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$6939万
+$50,800/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$6761万
+$48,256/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$6592万
+$48,256/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$6487万
+$46,300/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$6325万
+$46,300/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$6994万
+$49,920/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$6672万
+$48,842/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$6725万
+$48,000/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$6557万
+$48,000/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$6573万
+$46,915/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$6628万
+$48,521/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$6319万
+$45,100/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$7035万
+$51,503/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$6306万
+$45,007/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$6112万
+$44,746/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$6486万
+$46,298/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$6324万
+$46,298/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$6345万
+$45,291/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$6187万
+$45,291/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$5996万
+$42,800/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$7121万
+$52,128/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$5772万
+$41,200/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$6761万
+$49,492/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$6598万
+$47,095/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$6198万
+$45,375/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$5229万
+$37,323/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$6031万
+$44,153/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$6304万
+$45,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$4868万
+$35,637/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$6650万
+$47,466/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$6247万
+$45,731/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$6969万
+$49,742/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$6726万
+$49,239/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+$6641万
+$47,400/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+$6448万
+$47,200/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr"/>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 1366呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>6座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>SKYPLEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>SKYPLEX | 3203呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr"/>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 1401呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 1374呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Mansion 1 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>SKY MANOR</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>SKYPLEX</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>V. HOUSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>5&amp;6</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>SKYPLEX | 2437呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>SKY MANOR | 3099呎 (4+房)
+$24792万
+$80,000/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>B1&amp;G&amp;1-3</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>V. HOUSE | 4395呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Mansion 2 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>H. HOUSE</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>MANOR A</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>MANOR B</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>MANOR C</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>SKYPLEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>SKYPLEX | 2214呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>5&amp;6</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 1676呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 2034呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>MANOR C | 2090呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 1676呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 2114呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>MANOR C | 1986呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>B1&amp;G&amp;1-3</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>H. HOUSE | 4608呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-天玺．海第1期.xlsx
+++ b/files/九龙-启德-天玺．海第1期.xlsx
@@ -668,7 +668,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-启德-天玺．海第1期.xlsx
+++ b/files/九龙-启德-天玺．海第1期.xlsx
@@ -658,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J258"/>
+  <dimension ref="A1:N258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -671,6 +671,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -728,6 +732,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -778,6 +802,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -828,6 +872,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -878,6 +942,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -928,6 +1012,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -978,6 +1082,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1024,6 +1148,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1074,6 +1218,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1124,6 +1288,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1174,6 +1358,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1220,6 +1424,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1266,6 +1490,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1312,6 +1556,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1362,6 +1626,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1408,6 +1692,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1458,6 +1762,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1504,6 +1828,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1550,6 +1894,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1596,6 +1960,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1642,6 +2026,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1688,6 +2092,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1734,6 +2158,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1780,6 +2224,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1830,6 +2294,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1876,6 +2360,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1922,6 +2426,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1968,6 +2492,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2014,6 +2558,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2060,6 +2624,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2106,6 +2690,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2152,6 +2756,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2202,6 +2826,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2248,6 +2892,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2298,6 +2962,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2344,6 +3028,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2394,6 +3098,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2440,6 +3164,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2490,6 +3234,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2540,6 +3304,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2590,6 +3374,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2640,6 +3444,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2690,6 +3514,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2740,6 +3584,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2790,6 +3654,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2840,6 +3724,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2890,6 +3794,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2940,6 +3864,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2990,6 +3934,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3020,27 +3984,43 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>39855000</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>36101</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3090,6 +4070,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3136,6 +4136,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3186,6 +4206,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3232,6 +4272,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3282,6 +4342,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3332,6 +4412,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3382,6 +4482,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3432,6 +4552,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3482,6 +4622,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3532,6 +4692,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3582,6 +4762,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3632,6 +4832,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3682,6 +4902,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3732,6 +4972,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3782,6 +5042,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3832,6 +5112,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3882,6 +5182,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3932,6 +5252,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3982,6 +5322,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4032,6 +5392,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4082,6 +5462,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4132,6 +5532,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4182,6 +5602,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4232,6 +5672,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4282,6 +5742,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4332,6 +5812,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4378,6 +5878,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4428,6 +5948,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4478,6 +6018,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4528,6 +6088,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4578,6 +6158,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4628,6 +6228,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4678,6 +6298,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4728,6 +6368,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4778,6 +6438,26 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4828,6 +6508,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4878,6 +6578,26 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4928,6 +6648,26 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4978,6 +6718,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5028,6 +6788,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5078,6 +6858,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5128,6 +6928,26 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5178,6 +6998,26 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -5228,6 +7068,26 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5278,6 +7138,26 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5328,6 +7208,26 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5378,6 +7278,26 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5428,6 +7348,26 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5478,6 +7418,26 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5528,6 +7488,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5578,6 +7558,26 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5628,6 +7628,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5678,6 +7698,26 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5728,6 +7768,26 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5778,6 +7838,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5828,6 +7908,26 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5878,6 +7978,26 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5928,6 +8048,26 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5978,6 +8118,26 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6028,6 +8188,26 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6078,6 +8258,26 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6128,6 +8328,26 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6178,6 +8398,26 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6228,6 +8468,26 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6278,6 +8538,26 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6328,6 +8608,26 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6378,6 +8678,26 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6428,6 +8748,26 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6474,6 +8814,26 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6520,6 +8880,26 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6566,6 +8946,26 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6612,6 +9012,26 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6658,6 +9078,26 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6704,6 +9144,26 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6750,6 +9210,26 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6796,6 +9276,26 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6842,6 +9342,26 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6888,6 +9408,26 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6934,6 +9474,26 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6980,6 +9540,26 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7026,6 +9606,26 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7072,6 +9672,26 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7118,6 +9738,26 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7164,6 +9804,26 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7210,6 +9870,26 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7256,6 +9936,26 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7302,6 +10002,26 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7348,6 +10068,26 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7394,6 +10134,26 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7440,6 +10200,26 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7486,6 +10266,26 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7532,6 +10332,26 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7578,6 +10398,26 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7624,6 +10464,26 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7670,6 +10530,26 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7716,6 +10596,26 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7762,6 +10662,26 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7808,6 +10728,26 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7854,6 +10794,26 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7900,6 +10860,26 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7946,6 +10926,26 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7996,6 +10996,26 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -8042,6 +11062,26 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8092,6 +11132,26 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8142,6 +11202,26 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8192,6 +11272,26 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8242,6 +11342,26 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8292,6 +11412,26 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8342,6 +11482,26 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8392,6 +11552,26 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8442,6 +11622,26 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8488,6 +11688,26 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8538,6 +11758,26 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8584,6 +11824,26 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8630,6 +11890,26 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8676,6 +11956,26 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8722,6 +12022,26 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8768,6 +12088,26 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8814,6 +12154,26 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8860,6 +12220,26 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8906,6 +12286,26 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8952,6 +12352,26 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8998,6 +12418,26 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L173" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9044,6 +12484,26 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L174" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9090,6 +12550,26 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9136,6 +12616,26 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9182,6 +12682,26 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L177" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9228,6 +12748,26 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L178" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9274,6 +12814,26 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9320,6 +12880,26 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9366,6 +12946,26 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L181" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9412,6 +13012,26 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L182" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9458,6 +13078,26 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L183" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9504,6 +13144,26 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L184" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9550,6 +13210,26 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L185" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9596,6 +13276,26 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L186" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9642,6 +13342,26 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L187" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9688,6 +13408,26 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9734,6 +13474,26 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L189" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9780,6 +13540,26 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9826,6 +13606,26 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L191" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9872,6 +13672,26 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L192" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9918,6 +13738,26 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L193" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9964,6 +13804,26 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L194" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10010,6 +13870,26 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L195" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10056,6 +13936,26 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L196" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10102,6 +14002,26 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L197" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10148,6 +14068,26 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L198" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10194,6 +14134,26 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L199" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10240,6 +14200,26 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L200" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10290,6 +14270,26 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L201" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10340,6 +14340,26 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L202" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10390,6 +14410,26 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L203" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10440,6 +14480,26 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L204" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10490,6 +14550,26 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L205" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10540,6 +14620,26 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L206" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10590,6 +14690,26 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L207" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10640,6 +14760,26 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L208" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10690,6 +14830,26 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L209" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10740,6 +14900,26 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L210" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10790,6 +14970,26 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L211" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10840,6 +15040,26 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L212" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10890,6 +15110,26 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L213" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10940,6 +15180,26 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L214" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10990,6 +15250,26 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L215" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11040,6 +15320,26 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L216" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11090,6 +15390,26 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L217" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11140,6 +15460,26 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L218" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11190,6 +15530,26 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L219" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11240,6 +15600,26 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L220" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11290,6 +15670,26 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L221" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11340,6 +15740,26 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L222" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11390,6 +15810,26 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L223" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11440,6 +15880,26 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L224" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11490,6 +15950,26 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L225" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11540,6 +16020,26 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L226" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11590,6 +16090,26 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L227" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11640,6 +16160,26 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L228" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11690,6 +16230,26 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L229" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11740,6 +16300,26 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L230" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11790,6 +16370,26 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L231" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11840,6 +16440,26 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L232" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11890,6 +16510,26 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L233" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11940,6 +16580,26 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L234" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11990,6 +16650,26 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L235" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12040,6 +16720,26 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L236" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12090,6 +16790,26 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L237" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12140,6 +16860,26 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L238" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12190,6 +16930,26 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L239" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12240,6 +17000,26 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L240" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12290,6 +17070,26 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L241" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12340,6 +17140,26 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L242" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12390,6 +17210,26 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L243" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12440,6 +17280,26 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L244" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12490,6 +17350,26 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L245" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12540,6 +17420,26 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L246" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12590,6 +17490,26 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L247" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12640,6 +17560,26 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L248" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12686,6 +17626,26 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L249" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12736,6 +17696,26 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L250" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12786,6 +17766,26 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L251" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12836,6 +17836,26 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L252" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12886,6 +17906,26 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L253" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12936,6 +17976,26 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L254" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12986,6 +18046,26 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L255" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13036,6 +18116,26 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L256" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13086,6 +18186,26 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L257" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13136,13 +18256,33 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L258" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -13335,7 +18475,7 @@
           <t>A | 2141呎 (4+房)
 $13916万
 $65,000/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -13385,7 +18525,7 @@
           <t>A | 2175呎 (4+房)
 $12000万
 $55,172/呎
-(24年-07月)</t>
+(24年-07月-28日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -13410,7 +18550,7 @@
           <t>A | 2187呎 (4+房)
 $12089万
 $55,276/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -13418,7 +18558,7 @@
           <t>B | 1408呎 (4+房)
 $6663万
 $47,325/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -13435,7 +18575,7 @@
           <t>A | 2194呎 (4+房)
 $11672万
 $53,200/呎
-(24年-05月)</t>
+(24年-05月-12日)</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -13460,7 +18600,7 @@
           <t>A | 2196呎 (4+房)
 $11931万
 $54,330/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -13485,7 +18625,7 @@
           <t>A | 2192呎 (4+房)
 $11903万
 $54,300/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -13493,7 +18633,7 @@
           <t>B | 1408呎 (4+房)
 $6970万
 $49,500/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr"/>
@@ -13510,7 +18650,7 @@
           <t>A | 2183呎 (4+房)
 $11635万
 $53,300/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -13518,7 +18658,7 @@
           <t>B | 1408呎 (4+房)
 $6054万
 $43,000/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr"/>
@@ -13535,7 +18675,7 @@
           <t>A | 2171呎 (4+房)
 $11545万
 $53,180/呎
-(24年-11月)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -13543,7 +18683,7 @@
           <t>B | 1408呎 (4+房)
 $5984万
 $42,500/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr"/>
@@ -13560,7 +18700,7 @@
           <t>A | 2157呎 (4+房)
 $11356万
 $52,646/呎
-(24年-06月)</t>
+(24年-06月-13日)</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -13585,7 +18725,7 @@
           <t>A | 2143呎 (4+房)
 $11529万
 $53,800/呎
-(24年-07月)</t>
+(24年-07月-16日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -13593,7 +18733,7 @@
           <t>B | 1408呎 (4+房)
 $6619万
 $47,010/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr"/>
@@ -13610,7 +18750,7 @@
           <t>A | 2129呎 (4+房)
 $10928万
 $51,329/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -13618,7 +18758,7 @@
           <t>B | 1408呎 (4+房)
 $6786万
 $48,200/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr"/>
@@ -13635,7 +18775,7 @@
           <t>A | 2115呎 (4+房)
 $10300万
 $48,700/呎
-(25年-07月)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -13643,7 +18783,7 @@
           <t>B | 1408呎 (4+房)
 $5892万
 $41,844/呎
-(25年-07月)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr"/>
@@ -13660,7 +18800,7 @@
           <t>A | 2103呎 (4+房)
 $11551万
 $54,927/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -13685,7 +18825,7 @@
           <t>A | 2096呎 (4+房)
 $12164万
 $58,033/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -13710,7 +18850,7 @@
           <t>A | 2093呎 (4+房)
 $11822万
 $56,484/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -13882,12 +19022,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -13986,12 +19126,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
-招标单位
--
-(暂停销售)</t>
+$3986万
+$36,101/呎
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -14017,7 +19157,7 @@
           <t>A | 1104呎 (4+房)
 $3346万
 $30,310/呎
-(24年-05月)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -14043,7 +19183,7 @@
           <t>A | 1104呎 (4+房)
 $3312万
 $30,000/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -14262,7 +19402,7 @@
           <t>A | 1104呎 (4+房)
 $3950万
 $35,779/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -14845,7 +19985,7 @@
           <t>SKY MANOR | 2191呎 (4+房)
 $14887万
 $67,946/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr"/>
@@ -14861,7 +20001,7 @@
           <t>A | 1126呎 (4+房)
 $4281万
 $38,022/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -14869,7 +20009,7 @@
           <t>B | 1089呎 (4+房)
 $4636万
 $42,571/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -14886,7 +20026,7 @@
           <t>A | 1126呎 (4+房)
 $4135万
 $36,723/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -14894,7 +20034,7 @@
           <t>B | 1089呎 (4+房)
 $3780万
 $34,711/呎
-(24年-05月)</t>
+(24年-05月-05日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -14911,7 +20051,7 @@
           <t>A | 1126呎 (4+房)
 $4010万
 $35,613/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -14919,7 +20059,7 @@
           <t>B | 1089呎 (4+房)
 $4487万
 $41,201/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -14936,7 +20076,7 @@
           <t>A | 1126呎 (4+房)
 $4120万
 $36,590/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -14944,7 +20084,7 @@
           <t>B | 1089呎 (4+房)
 $3907万
 $35,875/呎
-(25年-01月)</t>
+(25年-01月-20日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -14961,7 +20101,7 @@
           <t>A | 1126呎 (4+房)
 $4175万
 $37,075/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -14969,7 +20109,7 @@
           <t>B | 1089呎 (4+房)
 $3719万
 $34,151/呎
-(24年-12月)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -14986,7 +20126,7 @@
           <t>A | 1126呎 (4+房)
 $4296万
 $38,156/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -14994,7 +20134,7 @@
           <t>B | 1089呎 (4+房)
 $3897万
 $35,781/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr"/>
@@ -15011,7 +20151,7 @@
           <t>A | 1126呎 (4+房)
 $4238万
 $37,638/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -15019,7 +20159,7 @@
           <t>B | 1089呎 (4+房)
 $3664万
 $33,650/呎
-(24年-12月)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr"/>
@@ -15036,7 +20176,7 @@
           <t>A | 1126呎 (4+房)
 $4179万
 $37,114/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -15044,7 +20184,7 @@
           <t>B | 1089呎 (4+房)
 $3858万
 $35,425/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr"/>
@@ -15061,7 +20201,7 @@
           <t>A | 1126呎 (4+房)
 $4000万
 $35,524/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -15069,7 +20209,7 @@
           <t>B | 1089呎 (4+房)
 $3572万
 $32,801/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr"/>
@@ -15086,7 +20226,7 @@
           <t>A | 1126呎 (4+房)
 $4132万
 $36,701/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -15094,7 +20234,7 @@
           <t>B | 1089呎 (4+房)
 $3539万
 $32,500/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr"/>
@@ -15111,7 +20251,7 @@
           <t>A | 1126呎 (4+房)
 $3892万
 $34,563/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -15119,7 +20259,7 @@
           <t>B | 1089呎 (4+房)
 $3529万
 $32,405/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr"/>
@@ -15136,7 +20276,7 @@
           <t>A | 1126呎 (4+房)
 $3738万
 $33,197/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -15144,7 +20284,7 @@
           <t>B | 1089呎 (4+房)
 $3508万
 $32,209/呎
-(24年-07月)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr"/>
@@ -15161,7 +20301,7 @@
           <t>A | 1126呎 (4+房)
 $3956万
 $35,133/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -15169,7 +20309,7 @@
           <t>B | 1089呎 (4+房)
 $3768万
 $34,601/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr"/>
@@ -15186,7 +20326,7 @@
           <t>A | 1126呎 (4+房)
 $3929万
 $34,898/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -15194,7 +20334,7 @@
           <t>B | 1089呎 (4+房)
 $3700万
 $33,976/呎
-(24年-07月)</t>
+(24年-07月-21日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr"/>
@@ -15211,7 +20351,7 @@
           <t>A | 1126呎 (4+房)
 $3850万
 $34,192/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -15219,7 +20359,7 @@
           <t>B | 1089呎 (4+房)
 $3659万
 $33,600/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr"/>
@@ -15236,7 +20376,7 @@
           <t>A | 1126呎 (4+房)
 $3378万
 $30,000/呎
-(25年-01月)</t>
+(25年-01月-22日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -15244,7 +20384,7 @@
           <t>B | 1089呎 (4+房)
 $3200万
 $29,385/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr"/>
@@ -15261,7 +20401,7 @@
           <t>A | 1126呎 (4+房)
 $3278万
 $29,115/呎
-(25年-01月)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -15505,7 +20645,7 @@
           <t>SKYPLEX | 3156呎 (4+房)
 $23039万
 $73,000/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -15520,7 +20660,7 @@
           <t>A | 1401呎 (4+房)
 $7155万
 $51,069/呎
-(24年-11月)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -15544,7 +20684,7 @@
           <t>A | 1401呎 (4+房)
 $7117万
 $50,800/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -15552,7 +20692,7 @@
           <t>B | 1366呎 (4+房)
 $6939万
 $50,800/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -15568,7 +20708,7 @@
           <t>A | 1401呎 (4+房)
 $6761万
 $48,256/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -15576,7 +20716,7 @@
           <t>B | 1366呎 (4+房)
 $6592万
 $48,256/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -15592,7 +20732,7 @@
           <t>A | 1401呎 (4+房)
 $6487万
 $46,300/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -15600,7 +20740,7 @@
           <t>B | 1366呎 (4+房)
 $6325万
 $46,300/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -15616,7 +20756,7 @@
           <t>A | 1401呎 (4+房)
 $6994万
 $49,920/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -15624,7 +20764,7 @@
           <t>B | 1366呎 (4+房)
 $6672万
 $48,842/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -15640,7 +20780,7 @@
           <t>A | 1401呎 (4+房)
 $6725万
 $48,000/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -15648,7 +20788,7 @@
           <t>B | 1366呎 (4+房)
 $6557万
 $48,000/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -15664,7 +20804,7 @@
           <t>A | 1401呎 (4+房)
 $6573万
 $46,915/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -15672,7 +20812,7 @@
           <t>B | 1366呎 (4+房)
 $6628万
 $48,521/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr"/>
@@ -15688,7 +20828,7 @@
           <t>A | 1401呎 (4+房)
 $6319万
 $45,100/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -15696,7 +20836,7 @@
           <t>B | 1366呎 (4+房)
 $7035万
 $51,503/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr"/>
@@ -15712,7 +20852,7 @@
           <t>A | 1401呎 (4+房)
 $6306万
 $45,007/呎
-(24年-05月)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -15720,7 +20860,7 @@
           <t>B | 1366呎 (4+房)
 $6112万
 $44,746/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr"/>
@@ -15736,7 +20876,7 @@
           <t>A | 1401呎 (4+房)
 $6486万
 $46,298/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -15744,7 +20884,7 @@
           <t>B | 1366呎 (4+房)
 $6324万
 $46,298/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr"/>
@@ -15760,7 +20900,7 @@
           <t>A | 1401呎 (4+房)
 $6345万
 $45,291/呎
-(24年-05月)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -15768,7 +20908,7 @@
           <t>B | 1366呎 (4+房)
 $6187万
 $45,291/呎
-(24年-05月)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr"/>
@@ -15784,7 +20924,7 @@
           <t>A | 1401呎 (4+房)
 $5996万
 $42,800/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -15792,7 +20932,7 @@
           <t>B | 1366呎 (4+房)
 $7121万
 $52,128/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr"/>
@@ -15808,7 +20948,7 @@
           <t>A | 1401呎 (4+房)
 $5772万
 $41,200/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -15816,7 +20956,7 @@
           <t>B | 1366呎 (4+房)
 $6761万
 $49,492/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr"/>
@@ -15832,7 +20972,7 @@
           <t>A | 1401呎 (4+房)
 $6598万
 $47,095/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -15840,7 +20980,7 @@
           <t>B | 1366呎 (4+房)
 $6198万
 $45,375/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr"/>
@@ -15856,7 +20996,7 @@
           <t>A | 1401呎 (4+房)
 $5229万
 $37,323/呎
-(25年-06月)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -15864,7 +21004,7 @@
           <t>B | 1366呎 (4+房)
 $6031万
 $44,153/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr"/>
@@ -15880,7 +21020,7 @@
           <t>A | 1401呎 (4+房)
 $6304万
 $45,000/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -15888,7 +21028,7 @@
           <t>B | 1366呎 (4+房)
 $4868万
 $35,637/呎
-(25年-04月)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr"/>
@@ -15904,7 +21044,7 @@
           <t>A | 1401呎 (4+房)
 $6650万
 $47,466/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -15912,7 +21052,7 @@
           <t>B | 1366呎 (4+房)
 $6247万
 $45,731/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr"/>
@@ -15928,7 +21068,7 @@
           <t>A | 1401呎 (4+房)
 $6969万
 $49,742/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -15936,7 +21076,7 @@
           <t>B | 1366呎 (4+房)
 $6726万
 $49,239/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr"/>
@@ -15952,7 +21092,7 @@
           <t>A | 1401呎 (4+房)
 $6641万
 $47,400/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -15960,7 +21100,7 @@
           <t>B | 1366呎 (4+房)
 $6448万
 $47,200/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr"/>
@@ -16796,7 +21936,7 @@
           <t>SKY MANOR | 3099呎 (4+房)
 $24792万
 $80,000/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr"/>

--- a/files/九龙-启德-天玺．海第1期.xlsx
+++ b/files/九龙-启德-天玺．海第1期.xlsx
@@ -1606,7 +1606,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2274,23 +2274,19 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>71100000</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>50497</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2299,12 +2295,12 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -2314,7 +2310,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18352,7 +18348,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18362,12 +18358,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -18578,12 +18574,12 @@
 (24年-05月-12日)</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr"/>
@@ -18703,12 +18699,12 @@
 (24年-06月-13日)</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
-招标单位
--
-(在售)</t>
+$7110万
+$50,497/呎
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr"/>

--- a/files/九龙-启德-天玺．海第1期.xlsx
+++ b/files/九龙-启德-天玺．海第1期.xlsx
@@ -26,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -138,6 +138,11 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
       <sz val="8"/>
@@ -219,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -290,7 +295,10 @@
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1338,7 +1346,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1348,12 +1356,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1363,12 +1371,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1378,7 +1386,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1606,23 +1614,19 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>70973200</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>50407</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1631,12 +1635,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1646,7 +1650,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1746,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1752,12 +1756,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1767,12 +1771,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -1782,7 +1786,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18353,17 +18357,17 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -18471,7 +18475,7 @@
           <t>A | 2141呎 (4+房)
 $13916万
 $65,000/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -18521,15 +18525,15 @@
           <t>A | 2175呎 (4+房)
 $12000万
 $55,172/呎
-(24年-07月-28日)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
--
--
-(暂停销售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -18546,7 +18550,7 @@
           <t>A | 2187呎 (4+房)
 $12089万
 $55,276/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -18554,7 +18558,7 @@
           <t>B | 1408呎 (4+房)
 $6663万
 $47,325/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -18571,15 +18575,15 @@
           <t>A | 2194呎 (4+房)
 $11672万
 $53,200/呎
-(24年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
-招标单位
--
-(暂停销售)</t>
+$7097万
+$50,407/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr"/>
@@ -18596,15 +18600,15 @@
           <t>A | 2196呎 (4+房)
 $11931万
 $54,330/呎
-(24年-12月-11日)</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
--
--
-(暂停销售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr"/>
@@ -18621,7 +18625,7 @@
           <t>A | 2192呎 (4+房)
 $11903万
 $54,300/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -18629,7 +18633,7 @@
           <t>B | 1408呎 (4+房)
 $6970万
 $49,500/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr"/>
@@ -18646,7 +18650,7 @@
           <t>A | 2183呎 (4+房)
 $11635万
 $53,300/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -18654,7 +18658,7 @@
           <t>B | 1408呎 (4+房)
 $6054万
 $43,000/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr"/>
@@ -18671,7 +18675,7 @@
           <t>A | 2171呎 (4+房)
 $11545万
 $53,180/呎
-(24年-11月-25日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -18679,7 +18683,7 @@
           <t>B | 1408呎 (4+房)
 $5984万
 $42,500/呎
-(25年-07月-23日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr"/>
@@ -18696,7 +18700,7 @@
           <t>A | 2157呎 (4+房)
 $11356万
 $52,646/呎
-(24年-06月-13日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -18704,7 +18708,7 @@
           <t>B | 1408呎 (4+房)
 $7110万
 $50,497/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr"/>
@@ -18721,7 +18725,7 @@
           <t>A | 2143呎 (4+房)
 $11529万
 $53,800/呎
-(24年-07月-16日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -18729,7 +18733,7 @@
           <t>B | 1408呎 (4+房)
 $6619万
 $47,010/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr"/>
@@ -18746,7 +18750,7 @@
           <t>A | 2129呎 (4+房)
 $10928万
 $51,329/呎
-(25年-02月-20日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -18754,7 +18758,7 @@
           <t>B | 1408呎 (4+房)
 $6786万
 $48,200/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr"/>
@@ -18771,7 +18775,7 @@
           <t>A | 2115呎 (4+房)
 $10300万
 $48,700/呎
-(25年-07月-21日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -18779,7 +18783,7 @@
           <t>B | 1408呎 (4+房)
 $5892万
 $41,844/呎
-(25年-07月-28日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr"/>
@@ -18796,7 +18800,7 @@
           <t>A | 2103呎 (4+房)
 $11551万
 $54,927/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -18821,10 +18825,10 @@
           <t>A | 2096呎 (4+房)
 $12164万
 $58,033/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 招标单位
@@ -18846,7 +18850,7 @@
           <t>A | 2093呎 (4+房)
 $11822万
 $56,484/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -18866,7 +18870,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>A | 2093呎 (4+房)
 招标单位
@@ -18874,7 +18878,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="25" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 招标单位
@@ -19127,7 +19131,7 @@
           <t>A | 1104呎 (4+房)
 $3986万
 $36,101/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -19153,7 +19157,7 @@
           <t>A | 1104呎 (4+房)
 $3346万
 $30,310/呎
-(24年-05月-02日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -19179,7 +19183,7 @@
           <t>A | 1104呎 (4+房)
 $3312万
 $30,000/呎
-(24年-10月-20日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -19218,7 +19222,7 @@
       </c>
       <c r="D10" s="20" t="inlineStr"/>
       <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="24" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>SKY MANOR | 998呎 (3房)
 招标单位
@@ -19233,7 +19237,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
 招标单位
@@ -19398,7 +19402,7 @@
           <t>A | 1104呎 (4+房)
 $3950万
 $35,779/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -19473,7 +19477,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
 招标单位
@@ -19553,7 +19557,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
 招标单位
@@ -19981,7 +19985,7 @@
           <t>SKY MANOR | 2191呎 (4+房)
 $14887万
 $67,946/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr"/>
@@ -19997,7 +20001,7 @@
           <t>A | 1126呎 (4+房)
 $4281万
 $38,022/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -20005,7 +20009,7 @@
           <t>B | 1089呎 (4+房)
 $4636万
 $42,571/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -20022,7 +20026,7 @@
           <t>A | 1126呎 (4+房)
 $4135万
 $36,723/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -20030,7 +20034,7 @@
           <t>B | 1089呎 (4+房)
 $3780万
 $34,711/呎
-(24年-05月-05日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -20047,7 +20051,7 @@
           <t>A | 1126呎 (4+房)
 $4010万
 $35,613/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -20055,7 +20059,7 @@
           <t>B | 1089呎 (4+房)
 $4487万
 $41,201/呎
-(26年-03月-12日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -20072,7 +20076,7 @@
           <t>A | 1126呎 (4+房)
 $4120万
 $36,590/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -20080,7 +20084,7 @@
           <t>B | 1089呎 (4+房)
 $3907万
 $35,875/呎
-(25年-01月-20日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -20097,7 +20101,7 @@
           <t>A | 1126呎 (4+房)
 $4175万
 $37,075/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -20105,7 +20109,7 @@
           <t>B | 1089呎 (4+房)
 $3719万
 $34,151/呎
-(24年-12月-12日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -20122,7 +20126,7 @@
           <t>A | 1126呎 (4+房)
 $4296万
 $38,156/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -20130,7 +20134,7 @@
           <t>B | 1089呎 (4+房)
 $3897万
 $35,781/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr"/>
@@ -20147,7 +20151,7 @@
           <t>A | 1126呎 (4+房)
 $4238万
 $37,638/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -20155,7 +20159,7 @@
           <t>B | 1089呎 (4+房)
 $3664万
 $33,650/呎
-(24年-12月-03日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr"/>
@@ -20172,7 +20176,7 @@
           <t>A | 1126呎 (4+房)
 $4179万
 $37,114/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -20180,7 +20184,7 @@
           <t>B | 1089呎 (4+房)
 $3858万
 $35,425/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr"/>
@@ -20197,7 +20201,7 @@
           <t>A | 1126呎 (4+房)
 $4000万
 $35,524/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -20205,7 +20209,7 @@
           <t>B | 1089呎 (4+房)
 $3572万
 $32,801/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr"/>
@@ -20222,7 +20226,7 @@
           <t>A | 1126呎 (4+房)
 $4132万
 $36,701/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -20230,7 +20234,7 @@
           <t>B | 1089呎 (4+房)
 $3539万
 $32,500/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr"/>
@@ -20247,7 +20251,7 @@
           <t>A | 1126呎 (4+房)
 $3892万
 $34,563/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -20255,7 +20259,7 @@
           <t>B | 1089呎 (4+房)
 $3529万
 $32,405/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr"/>
@@ -20272,7 +20276,7 @@
           <t>A | 1126呎 (4+房)
 $3738万
 $33,197/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -20280,7 +20284,7 @@
           <t>B | 1089呎 (4+房)
 $3508万
 $32,209/呎
-(24年-07月-03日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr"/>
@@ -20297,7 +20301,7 @@
           <t>A | 1126呎 (4+房)
 $3956万
 $35,133/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -20305,7 +20309,7 @@
           <t>B | 1089呎 (4+房)
 $3768万
 $34,601/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr"/>
@@ -20322,7 +20326,7 @@
           <t>A | 1126呎 (4+房)
 $3929万
 $34,898/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -20330,7 +20334,7 @@
           <t>B | 1089呎 (4+房)
 $3700万
 $33,976/呎
-(24年-07月-21日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr"/>
@@ -20347,7 +20351,7 @@
           <t>A | 1126呎 (4+房)
 $3850万
 $34,192/呎
-(24年-06月-04日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -20355,7 +20359,7 @@
           <t>B | 1089呎 (4+房)
 $3659万
 $33,600/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr"/>
@@ -20372,7 +20376,7 @@
           <t>A | 1126呎 (4+房)
 $3378万
 $30,000/呎
-(25年-01月-22日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -20380,7 +20384,7 @@
           <t>B | 1089呎 (4+房)
 $3200万
 $29,385/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr"/>
@@ -20397,10 +20401,10 @@
           <t>A | 1126呎 (4+房)
 $3278万
 $29,115/呎
-(25年-01月-14日)</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="inlineStr">
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C23" s="25" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 招标单位
@@ -20641,7 +20645,7 @@
           <t>SKYPLEX | 3156呎 (4+房)
 $23039万
 $73,000/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -20656,7 +20660,7 @@
           <t>A | 1401呎 (4+房)
 $7155万
 $51,069/呎
-(24年-11月-20日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -20680,7 +20684,7 @@
           <t>A | 1401呎 (4+房)
 $7117万
 $50,800/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -20688,7 +20692,7 @@
           <t>B | 1366呎 (4+房)
 $6939万
 $50,800/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -20704,7 +20708,7 @@
           <t>A | 1401呎 (4+房)
 $6761万
 $48,256/呎
-(24年-04月-25日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -20712,7 +20716,7 @@
           <t>B | 1366呎 (4+房)
 $6592万
 $48,256/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -20728,7 +20732,7 @@
           <t>A | 1401呎 (4+房)
 $6487万
 $46,300/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -20736,7 +20740,7 @@
           <t>B | 1366呎 (4+房)
 $6325万
 $46,300/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -20752,7 +20756,7 @@
           <t>A | 1401呎 (4+房)
 $6994万
 $49,920/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -20760,7 +20764,7 @@
           <t>B | 1366呎 (4+房)
 $6672万
 $48,842/呎
-(24年-04月-25日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -20776,7 +20780,7 @@
           <t>A | 1401呎 (4+房)
 $6725万
 $48,000/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -20784,7 +20788,7 @@
           <t>B | 1366呎 (4+房)
 $6557万
 $48,000/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -20800,7 +20804,7 @@
           <t>A | 1401呎 (4+房)
 $6573万
 $46,915/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -20808,7 +20812,7 @@
           <t>B | 1366呎 (4+房)
 $6628万
 $48,521/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr"/>
@@ -20824,7 +20828,7 @@
           <t>A | 1401呎 (4+房)
 $6319万
 $45,100/呎
-(25年-05月-20日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -20832,7 +20836,7 @@
           <t>B | 1366呎 (4+房)
 $7035万
 $51,503/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr"/>
@@ -20848,7 +20852,7 @@
           <t>A | 1401呎 (4+房)
 $6306万
 $45,007/呎
-(24年-05月-09日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -20856,7 +20860,7 @@
           <t>B | 1366呎 (4+房)
 $6112万
 $44,746/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr"/>
@@ -20872,7 +20876,7 @@
           <t>A | 1401呎 (4+房)
 $6486万
 $46,298/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -20880,7 +20884,7 @@
           <t>B | 1366呎 (4+房)
 $6324万
 $46,298/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr"/>
@@ -20896,7 +20900,7 @@
           <t>A | 1401呎 (4+房)
 $6345万
 $45,291/呎
-(24年-05月-08日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -20904,7 +20908,7 @@
           <t>B | 1366呎 (4+房)
 $6187万
 $45,291/呎
-(24年-05月-08日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr"/>
@@ -20920,7 +20924,7 @@
           <t>A | 1401呎 (4+房)
 $5996万
 $42,800/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -20928,7 +20932,7 @@
           <t>B | 1366呎 (4+房)
 $7121万
 $52,128/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr"/>
@@ -20944,7 +20948,7 @@
           <t>A | 1401呎 (4+房)
 $5772万
 $41,200/呎
-(24年-10月-23日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -20952,7 +20956,7 @@
           <t>B | 1366呎 (4+房)
 $6761万
 $49,492/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr"/>
@@ -20968,7 +20972,7 @@
           <t>A | 1401呎 (4+房)
 $6598万
 $47,095/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -20976,7 +20980,7 @@
           <t>B | 1366呎 (4+房)
 $6198万
 $45,375/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr"/>
@@ -20992,7 +20996,7 @@
           <t>A | 1401呎 (4+房)
 $5229万
 $37,323/呎
-(25年-06月-10日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -21000,7 +21004,7 @@
           <t>B | 1366呎 (4+房)
 $6031万
 $44,153/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr"/>
@@ -21016,7 +21020,7 @@
           <t>A | 1401呎 (4+房)
 $6304万
 $45,000/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -21024,7 +21028,7 @@
           <t>B | 1366呎 (4+房)
 $4868万
 $35,637/呎
-(25年-04月-15日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr"/>
@@ -21040,7 +21044,7 @@
           <t>A | 1401呎 (4+房)
 $6650万
 $47,466/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -21048,7 +21052,7 @@
           <t>B | 1366呎 (4+房)
 $6247万
 $45,731/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr"/>
@@ -21064,7 +21068,7 @@
           <t>A | 1401呎 (4+房)
 $6969万
 $49,742/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -21072,7 +21076,7 @@
           <t>B | 1366呎 (4+房)
 $6726万
 $49,239/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr"/>
@@ -21088,7 +21092,7 @@
           <t>A | 1401呎 (4+房)
 $6641万
 $47,400/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -21096,7 +21100,7 @@
           <t>B | 1366呎 (4+房)
 $6448万
 $47,200/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr"/>
@@ -21932,7 +21936,7 @@
           <t>SKY MANOR | 3099呎 (4+房)
 $24792万
 $80,000/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr"/>

--- a/files/九龙-启德-天玺．海第1期.xlsx
+++ b/files/九龙-启德-天玺．海第1期.xlsx
@@ -18475,7 +18475,7 @@
           <t>A | 2141呎 (4+房)
 $13916万
 $65,000/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -18525,7 +18525,7 @@
           <t>A | 2175呎 (4+房)
 $12000万
 $55,172/呎
-(24年-07月)</t>
+(24年-07月-28日)</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -18550,7 +18550,7 @@
           <t>A | 2187呎 (4+房)
 $12089万
 $55,276/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -18558,7 +18558,7 @@
           <t>B | 1408呎 (4+房)
 $6663万
 $47,325/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -18575,7 +18575,7 @@
           <t>A | 2194呎 (4+房)
 $11672万
 $53,200/呎
-(24年-05月)</t>
+(24年-05月-12日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -18583,7 +18583,7 @@
           <t>B | 1408呎 (4+房)
 $7097万
 $50,407/呎
-(26年-07月)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr"/>
@@ -18600,7 +18600,7 @@
           <t>A | 2196呎 (4+房)
 $11931万
 $54,330/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -18625,7 +18625,7 @@
           <t>A | 2192呎 (4+房)
 $11903万
 $54,300/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -18633,7 +18633,7 @@
           <t>B | 1408呎 (4+房)
 $6970万
 $49,500/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr"/>
@@ -18650,7 +18650,7 @@
           <t>A | 2183呎 (4+房)
 $11635万
 $53,300/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -18658,7 +18658,7 @@
           <t>B | 1408呎 (4+房)
 $6054万
 $43,000/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr"/>
@@ -18675,7 +18675,7 @@
           <t>A | 2171呎 (4+房)
 $11545万
 $53,180/呎
-(24年-11月)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -18683,7 +18683,7 @@
           <t>B | 1408呎 (4+房)
 $5984万
 $42,500/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr"/>
@@ -18700,7 +18700,7 @@
           <t>A | 2157呎 (4+房)
 $11356万
 $52,646/呎
-(24年-06月)</t>
+(24年-06月-13日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -18708,7 +18708,7 @@
           <t>B | 1408呎 (4+房)
 $7110万
 $50,497/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr"/>
@@ -18725,7 +18725,7 @@
           <t>A | 2143呎 (4+房)
 $11529万
 $53,800/呎
-(24年-07月)</t>
+(24年-07月-16日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -18733,7 +18733,7 @@
           <t>B | 1408呎 (4+房)
 $6619万
 $47,010/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr"/>
@@ -18750,7 +18750,7 @@
           <t>A | 2129呎 (4+房)
 $10928万
 $51,329/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -18758,7 +18758,7 @@
           <t>B | 1408呎 (4+房)
 $6786万
 $48,200/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr"/>
@@ -18775,7 +18775,7 @@
           <t>A | 2115呎 (4+房)
 $10300万
 $48,700/呎
-(25年-07月)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -18783,7 +18783,7 @@
           <t>B | 1408呎 (4+房)
 $5892万
 $41,844/呎
-(25年-07月)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr"/>
@@ -18800,7 +18800,7 @@
           <t>A | 2103呎 (4+房)
 $11551万
 $54,927/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -18825,7 +18825,7 @@
           <t>A | 2096呎 (4+房)
 $12164万
 $58,033/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="C22" s="25" t="inlineStr">
@@ -18850,7 +18850,7 @@
           <t>A | 2093呎 (4+房)
 $11822万
 $56,484/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -19131,7 +19131,7 @@
           <t>A | 1104呎 (4+房)
 $3986万
 $36,101/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -19157,7 +19157,7 @@
           <t>A | 1104呎 (4+房)
 $3346万
 $30,310/呎
-(24年-05月)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -19183,7 +19183,7 @@
           <t>A | 1104呎 (4+房)
 $3312万
 $30,000/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -19402,7 +19402,7 @@
           <t>A | 1104呎 (4+房)
 $3950万
 $35,779/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -19985,7 +19985,7 @@
           <t>SKY MANOR | 2191呎 (4+房)
 $14887万
 $67,946/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr"/>
@@ -20001,7 +20001,7 @@
           <t>A | 1126呎 (4+房)
 $4281万
 $38,022/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -20009,7 +20009,7 @@
           <t>B | 1089呎 (4+房)
 $4636万
 $42,571/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -20026,7 +20026,7 @@
           <t>A | 1126呎 (4+房)
 $4135万
 $36,723/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -20034,7 +20034,7 @@
           <t>B | 1089呎 (4+房)
 $3780万
 $34,711/呎
-(24年-05月)</t>
+(24年-05月-05日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -20051,7 +20051,7 @@
           <t>A | 1126呎 (4+房)
 $4010万
 $35,613/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -20059,7 +20059,7 @@
           <t>B | 1089呎 (4+房)
 $4487万
 $41,201/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -20076,7 +20076,7 @@
           <t>A | 1126呎 (4+房)
 $4120万
 $36,590/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -20084,7 +20084,7 @@
           <t>B | 1089呎 (4+房)
 $3907万
 $35,875/呎
-(25年-01月)</t>
+(25年-01月-20日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -20101,7 +20101,7 @@
           <t>A | 1126呎 (4+房)
 $4175万
 $37,075/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -20109,7 +20109,7 @@
           <t>B | 1089呎 (4+房)
 $3719万
 $34,151/呎
-(24年-12月)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -20126,7 +20126,7 @@
           <t>A | 1126呎 (4+房)
 $4296万
 $38,156/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -20134,7 +20134,7 @@
           <t>B | 1089呎 (4+房)
 $3897万
 $35,781/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr"/>
@@ -20151,7 +20151,7 @@
           <t>A | 1126呎 (4+房)
 $4238万
 $37,638/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -20159,7 +20159,7 @@
           <t>B | 1089呎 (4+房)
 $3664万
 $33,650/呎
-(24年-12月)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr"/>
@@ -20176,7 +20176,7 @@
           <t>A | 1126呎 (4+房)
 $4179万
 $37,114/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -20184,7 +20184,7 @@
           <t>B | 1089呎 (4+房)
 $3858万
 $35,425/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr"/>
@@ -20201,7 +20201,7 @@
           <t>A | 1126呎 (4+房)
 $4000万
 $35,524/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -20209,7 +20209,7 @@
           <t>B | 1089呎 (4+房)
 $3572万
 $32,801/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr"/>
@@ -20226,7 +20226,7 @@
           <t>A | 1126呎 (4+房)
 $4132万
 $36,701/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -20234,7 +20234,7 @@
           <t>B | 1089呎 (4+房)
 $3539万
 $32,500/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr"/>
@@ -20251,7 +20251,7 @@
           <t>A | 1126呎 (4+房)
 $3892万
 $34,563/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -20259,7 +20259,7 @@
           <t>B | 1089呎 (4+房)
 $3529万
 $32,405/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr"/>
@@ -20276,7 +20276,7 @@
           <t>A | 1126呎 (4+房)
 $3738万
 $33,197/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -20284,7 +20284,7 @@
           <t>B | 1089呎 (4+房)
 $3508万
 $32,209/呎
-(24年-07月)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr"/>
@@ -20301,7 +20301,7 @@
           <t>A | 1126呎 (4+房)
 $3956万
 $35,133/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -20309,7 +20309,7 @@
           <t>B | 1089呎 (4+房)
 $3768万
 $34,601/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr"/>
@@ -20326,7 +20326,7 @@
           <t>A | 1126呎 (4+房)
 $3929万
 $34,898/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -20334,7 +20334,7 @@
           <t>B | 1089呎 (4+房)
 $3700万
 $33,976/呎
-(24年-07月)</t>
+(24年-07月-21日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr"/>
@@ -20351,7 +20351,7 @@
           <t>A | 1126呎 (4+房)
 $3850万
 $34,192/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -20359,7 +20359,7 @@
           <t>B | 1089呎 (4+房)
 $3659万
 $33,600/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr"/>
@@ -20376,7 +20376,7 @@
           <t>A | 1126呎 (4+房)
 $3378万
 $30,000/呎
-(25年-01月)</t>
+(25年-01月-22日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -20384,7 +20384,7 @@
           <t>B | 1089呎 (4+房)
 $3200万
 $29,385/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr"/>
@@ -20401,7 +20401,7 @@
           <t>A | 1126呎 (4+房)
 $3278万
 $29,115/呎
-(25年-01月)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
       <c r="C23" s="25" t="inlineStr">
@@ -20645,7 +20645,7 @@
           <t>SKYPLEX | 3156呎 (4+房)
 $23039万
 $73,000/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -20660,7 +20660,7 @@
           <t>A | 1401呎 (4+房)
 $7155万
 $51,069/呎
-(24年-11月)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -20684,7 +20684,7 @@
           <t>A | 1401呎 (4+房)
 $7117万
 $50,800/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -20692,7 +20692,7 @@
           <t>B | 1366呎 (4+房)
 $6939万
 $50,800/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -20708,7 +20708,7 @@
           <t>A | 1401呎 (4+房)
 $6761万
 $48,256/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -20716,7 +20716,7 @@
           <t>B | 1366呎 (4+房)
 $6592万
 $48,256/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -20732,7 +20732,7 @@
           <t>A | 1401呎 (4+房)
 $6487万
 $46,300/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -20740,7 +20740,7 @@
           <t>B | 1366呎 (4+房)
 $6325万
 $46,300/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -20756,7 +20756,7 @@
           <t>A | 1401呎 (4+房)
 $6994万
 $49,920/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -20764,7 +20764,7 @@
           <t>B | 1366呎 (4+房)
 $6672万
 $48,842/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -20780,7 +20780,7 @@
           <t>A | 1401呎 (4+房)
 $6725万
 $48,000/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -20788,7 +20788,7 @@
           <t>B | 1366呎 (4+房)
 $6557万
 $48,000/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -20804,7 +20804,7 @@
           <t>A | 1401呎 (4+房)
 $6573万
 $46,915/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -20812,7 +20812,7 @@
           <t>B | 1366呎 (4+房)
 $6628万
 $48,521/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr"/>
@@ -20828,7 +20828,7 @@
           <t>A | 1401呎 (4+房)
 $6319万
 $45,100/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -20836,7 +20836,7 @@
           <t>B | 1366呎 (4+房)
 $7035万
 $51,503/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr"/>
@@ -20852,7 +20852,7 @@
           <t>A | 1401呎 (4+房)
 $6306万
 $45,007/呎
-(24年-05月)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -20860,7 +20860,7 @@
           <t>B | 1366呎 (4+房)
 $6112万
 $44,746/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr"/>
@@ -20876,7 +20876,7 @@
           <t>A | 1401呎 (4+房)
 $6486万
 $46,298/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -20884,7 +20884,7 @@
           <t>B | 1366呎 (4+房)
 $6324万
 $46,298/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr"/>
@@ -20900,7 +20900,7 @@
           <t>A | 1401呎 (4+房)
 $6345万
 $45,291/呎
-(24年-05月)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -20908,7 +20908,7 @@
           <t>B | 1366呎 (4+房)
 $6187万
 $45,291/呎
-(24年-05月)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr"/>
@@ -20924,7 +20924,7 @@
           <t>A | 1401呎 (4+房)
 $5996万
 $42,800/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -20932,7 +20932,7 @@
           <t>B | 1366呎 (4+房)
 $7121万
 $52,128/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr"/>
@@ -20948,7 +20948,7 @@
           <t>A | 1401呎 (4+房)
 $5772万
 $41,200/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -20956,7 +20956,7 @@
           <t>B | 1366呎 (4+房)
 $6761万
 $49,492/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr"/>
@@ -20972,7 +20972,7 @@
           <t>A | 1401呎 (4+房)
 $6598万
 $47,095/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -20980,7 +20980,7 @@
           <t>B | 1366呎 (4+房)
 $6198万
 $45,375/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr"/>
@@ -20996,7 +20996,7 @@
           <t>A | 1401呎 (4+房)
 $5229万
 $37,323/呎
-(25年-06月)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -21004,7 +21004,7 @@
           <t>B | 1366呎 (4+房)
 $6031万
 $44,153/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr"/>
@@ -21020,7 +21020,7 @@
           <t>A | 1401呎 (4+房)
 $6304万
 $45,000/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -21028,7 +21028,7 @@
           <t>B | 1366呎 (4+房)
 $4868万
 $35,637/呎
-(25年-04月)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr"/>
@@ -21044,7 +21044,7 @@
           <t>A | 1401呎 (4+房)
 $6650万
 $47,466/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -21052,7 +21052,7 @@
           <t>B | 1366呎 (4+房)
 $6247万
 $45,731/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr"/>
@@ -21068,7 +21068,7 @@
           <t>A | 1401呎 (4+房)
 $6969万
 $49,742/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -21076,7 +21076,7 @@
           <t>B | 1366呎 (4+房)
 $6726万
 $49,239/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr"/>
@@ -21092,7 +21092,7 @@
           <t>A | 1401呎 (4+房)
 $6641万
 $47,400/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -21100,7 +21100,7 @@
           <t>B | 1366呎 (4+房)
 $6448万
 $47,200/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr"/>
@@ -21936,7 +21936,7 @@
           <t>SKY MANOR | 3099呎 (4+房)
 $24792万
 $80,000/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr"/>

--- a/files/九龙-启德-天玺．海第1期.xlsx
+++ b/files/九龙-启德-天玺．海第1期.xlsx
@@ -26,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -138,11 +138,6 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
       <sz val="8"/>
@@ -224,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -295,10 +290,7 @@
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1346,7 +1338,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1746,7 +1738,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -17615,7 +17607,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -18352,12 +18344,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -18533,7 +18525,7 @@
           <t>B | 1408呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -18608,7 +18600,7 @@
           <t>B | 1408呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr"/>
@@ -18828,7 +18820,7 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 招标单位
@@ -18870,7 +18862,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>A | 2093呎 (4+房)
 招标单位
@@ -18878,7 +18870,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 招标单位
@@ -19222,7 +19214,7 @@
       </c>
       <c r="D10" s="20" t="inlineStr"/>
       <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="25" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>SKY MANOR | 998呎 (3房)
 招标单位
@@ -19237,7 +19229,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
 招标单位
@@ -19477,7 +19469,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
 招标单位
@@ -19557,7 +19549,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
 招标单位
@@ -20404,7 +20396,7 @@
 (25年-01月-14日)</t>
         </is>
       </c>
-      <c r="C23" s="25" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 招标单位
@@ -21936,7 +21928,7 @@
           <t>SKY MANOR | 3099呎 (4+房)
 $24792万
 $80,000/呎
-(26年-07月-05日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr"/>
